--- a/EKG_Kalite_Yönetim_Sistemi/98_Uygulama_Kayıtları/09_Risk Azaltma ve PFMEA/EKG-PRJ-FRM-04_proses_fmea__cfrl1_uygulama_ornegi.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/98_Uygulama_Kayıtları/09_Risk Azaltma ve PFMEA/EKG-PRJ-FRM-04_proses_fmea__cfrl1_uygulama_ornegi.xlsx
@@ -1394,7 +1394,8 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-PRJ-FRM-04&amp;C&amp;"Arial,Regular"&amp;11Proses FMEA - CFRL1 Uygulama Örneği</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 15.06.2026 | Revizyon: 29.09.2026
+Revizyon nedeni: Kaynak PFMEA tarihsel örnek olarak işaretlendi; otomatik risk kabulü kaldırıldı.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -2556,7 +2557,8 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-PRJ-FRM-04&amp;C&amp;"Arial,Regular"&amp;11Proses FMEA - CFRL1 Uygulama Örneği</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 15.06.2026 | Revizyon: 29.09.2026
+Revizyon nedeni: Kaynak PFMEA tarihsel örnek olarak işaretlendi; otomatik risk kabulü kaldırıldı.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>